--- a/缓存数据/enterpriseCsm.xlsx
+++ b/缓存数据/enterpriseCsm.xlsx
@@ -558,40 +558,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1222898.410000001</v>
+        <v>1240191.299999998</v>
       </c>
       <c r="C4" t="n">
-        <v>1448</v>
+        <v>1431</v>
       </c>
       <c r="D4" t="n">
-        <v>1065442.27</v>
+        <v>1059976.349999998</v>
       </c>
       <c r="E4" t="n">
-        <v>1418</v>
+        <v>1401</v>
       </c>
       <c r="F4" t="n">
-        <v>157456.1399999999</v>
+        <v>180214.9499999999</v>
       </c>
       <c r="G4" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H4" t="n">
-        <v>834539.7000000002</v>
+        <v>854032.8199999991</v>
       </c>
       <c r="I4" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J4" t="n">
-        <v>388358.7100000001</v>
+        <v>386158.4800000001</v>
       </c>
       <c r="K4" t="n">
-        <v>1328</v>
+        <v>1312</v>
       </c>
       <c r="L4" t="n">
-        <v>18733.36</v>
+        <v>18775.58000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5">
@@ -601,40 +601,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1240191.299999998</v>
+        <v>1234683.380000001</v>
       </c>
       <c r="C5" t="n">
-        <v>1431</v>
+        <v>1444</v>
       </c>
       <c r="D5" t="n">
-        <v>1059976.349999998</v>
+        <v>1025987.569999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1401</v>
+        <v>1414</v>
       </c>
       <c r="F5" t="n">
-        <v>180214.9499999999</v>
+        <v>208695.81</v>
       </c>
       <c r="G5" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H5" t="n">
-        <v>854032.8199999998</v>
+        <v>847067.5600000004</v>
       </c>
       <c r="I5" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="J5" t="n">
-        <v>386158.4800000004</v>
+        <v>387615.8200000001</v>
       </c>
       <c r="K5" t="n">
-        <v>1311</v>
+        <v>1327</v>
       </c>
       <c r="L5" t="n">
-        <v>18775.58</v>
+        <v>18830.08</v>
       </c>
       <c r="M5" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
@@ -644,40 +644,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1234683.380000002</v>
+        <v>1185116.01</v>
       </c>
       <c r="C6" t="n">
-        <v>1444</v>
+        <v>1298</v>
       </c>
       <c r="D6" t="n">
-        <v>1025987.57</v>
+        <v>972923.4899999981</v>
       </c>
       <c r="E6" t="n">
-        <v>1414</v>
+        <v>1271</v>
       </c>
       <c r="F6" t="n">
-        <v>208695.81</v>
+        <v>212192.52</v>
       </c>
       <c r="G6" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H6" t="n">
-        <v>847067.5599999998</v>
+        <v>857460.2199999997</v>
       </c>
       <c r="I6" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J6" t="n">
-        <v>387615.8200000001</v>
+        <v>327655.7900000004</v>
       </c>
       <c r="K6" t="n">
-        <v>1326</v>
+        <v>1178</v>
       </c>
       <c r="L6" t="n">
-        <v>18830.08</v>
+        <v>18413.58000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -687,37 +687,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1185116.009999999</v>
+        <v>1156915.85</v>
       </c>
       <c r="C7" t="n">
-        <v>1298</v>
+        <v>1209</v>
       </c>
       <c r="D7" t="n">
-        <v>972923.489999998</v>
+        <v>972335.7900000005</v>
       </c>
       <c r="E7" t="n">
-        <v>1271</v>
+        <v>1176</v>
       </c>
       <c r="F7" t="n">
-        <v>212192.52</v>
+        <v>184580.06</v>
       </c>
       <c r="G7" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H7" t="n">
-        <v>857460.2199999995</v>
+        <v>872389.45</v>
       </c>
       <c r="I7" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J7" t="n">
-        <v>327655.7900000002</v>
+        <v>284526.4000000008</v>
       </c>
       <c r="K7" t="n">
-        <v>1177</v>
+        <v>1092</v>
       </c>
       <c r="L7" t="n">
-        <v>18413.58</v>
+        <v>18361.19</v>
       </c>
       <c r="M7" t="n">
         <v>66</v>
@@ -730,40 +730,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1156915.85</v>
+        <v>1226590.020000001</v>
       </c>
       <c r="C8" t="n">
-        <v>1209</v>
+        <v>1435</v>
       </c>
       <c r="D8" t="n">
-        <v>972335.7900000003</v>
+        <v>1054734.900000003</v>
       </c>
       <c r="E8" t="n">
-        <v>1176</v>
+        <v>1404</v>
       </c>
       <c r="F8" t="n">
-        <v>184580.06</v>
+        <v>171855.1199999999</v>
       </c>
       <c r="G8" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H8" t="n">
-        <v>872389.4499999997</v>
+        <v>845689.2200000003</v>
       </c>
       <c r="I8" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J8" t="n">
-        <v>284526.4000000003</v>
+        <v>380900.7999999997</v>
       </c>
       <c r="K8" t="n">
-        <v>1091</v>
+        <v>1313</v>
       </c>
       <c r="L8" t="n">
-        <v>18361.19</v>
+        <v>20034.45</v>
       </c>
       <c r="M8" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
@@ -773,40 +773,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1226590.020000002</v>
+        <v>1199019.850000002</v>
       </c>
       <c r="C9" t="n">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="D9" t="n">
-        <v>1054734.900000002</v>
+        <v>1024025.000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="F9" t="n">
-        <v>171855.1199999999</v>
+        <v>174994.8499999998</v>
       </c>
       <c r="G9" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H9" t="n">
-        <v>845689.2200000003</v>
+        <v>816042.5000000006</v>
       </c>
       <c r="I9" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J9" t="n">
-        <v>380900.8000000003</v>
+        <v>382977.3499999999</v>
       </c>
       <c r="K9" t="n">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="L9" t="n">
-        <v>20034.45</v>
+        <v>19911.35</v>
       </c>
       <c r="M9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -816,40 +816,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1199019.850000001</v>
+        <v>1235058.840000003</v>
       </c>
       <c r="C10" t="n">
-        <v>1433</v>
+        <v>1443</v>
       </c>
       <c r="D10" t="n">
-        <v>1024025</v>
+        <v>1044756.860000001</v>
       </c>
       <c r="E10" t="n">
-        <v>1403</v>
+        <v>1413</v>
       </c>
       <c r="F10" t="n">
-        <v>174994.8499999998</v>
+        <v>190301.9800000001</v>
       </c>
       <c r="G10" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H10" t="n">
-        <v>816042.5000000002</v>
+        <v>837111.9800000001</v>
       </c>
       <c r="I10" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="J10" t="n">
-        <v>382977.3499999996</v>
+        <v>397946.8599999999</v>
       </c>
       <c r="K10" t="n">
-        <v>1313</v>
+        <v>1326</v>
       </c>
       <c r="L10" t="n">
-        <v>19911.34999999999</v>
+        <v>20033.10999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -859,37 +859,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1235058.84</v>
+        <v>1274706.210000002</v>
       </c>
       <c r="C11" t="n">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="D11" t="n">
-        <v>1044756.860000002</v>
+        <v>1073870.639999999</v>
       </c>
       <c r="E11" t="n">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="F11" t="n">
-        <v>190301.9800000001</v>
+        <v>200835.5700000001</v>
       </c>
       <c r="G11" t="n">
         <v>86</v>
       </c>
       <c r="H11" t="n">
-        <v>837111.9800000002</v>
+        <v>865382.9099999986</v>
       </c>
       <c r="I11" t="n">
         <v>118</v>
       </c>
       <c r="J11" t="n">
-        <v>397946.8599999998</v>
+        <v>409323.3000000003</v>
       </c>
       <c r="K11" t="n">
-        <v>1325</v>
+        <v>1319</v>
       </c>
       <c r="L11" t="n">
-        <v>20033.10999999999</v>
+        <v>19794.95</v>
       </c>
       <c r="M11" t="n">
         <v>73</v>

--- a/缓存数据/enterpriseCsm.xlsx
+++ b/缓存数据/enterpriseCsm.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74,18 +74,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -558,40 +558,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1240191.299999998</v>
+        <v>1862405.719999996</v>
       </c>
       <c r="C4" t="n">
-        <v>1431</v>
+        <v>1468</v>
       </c>
       <c r="D4" t="n">
-        <v>1059976.349999998</v>
+        <v>1624351.509999997</v>
       </c>
       <c r="E4" t="n">
-        <v>1401</v>
+        <v>1442</v>
       </c>
       <c r="F4" t="n">
-        <v>180214.9499999999</v>
+        <v>238054.21</v>
       </c>
       <c r="G4" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="H4" t="n">
-        <v>854032.8199999991</v>
+        <v>872318.6900000003</v>
       </c>
       <c r="I4" t="n">
         <v>119</v>
       </c>
       <c r="J4" t="n">
-        <v>386158.4800000001</v>
+        <v>990087.0300000014</v>
       </c>
       <c r="K4" t="n">
-        <v>1312</v>
+        <v>1349</v>
       </c>
       <c r="L4" t="n">
-        <v>18775.58000000001</v>
+        <v>125319.72</v>
       </c>
       <c r="M4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5">
@@ -601,40 +601,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1234683.380000001</v>
+        <v>3388229.190000007</v>
       </c>
       <c r="C5" t="n">
-        <v>1444</v>
+        <v>1493</v>
       </c>
       <c r="D5" t="n">
-        <v>1025987.569999999</v>
+        <v>3179629.170000006</v>
       </c>
       <c r="E5" t="n">
-        <v>1414</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="n">
-        <v>208695.81</v>
+        <v>208600.0199999999</v>
       </c>
       <c r="G5" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="H5" t="n">
-        <v>847067.5600000004</v>
+        <v>845688.8399999995</v>
       </c>
       <c r="I5" t="n">
         <v>117</v>
       </c>
       <c r="J5" t="n">
-        <v>387615.8200000001</v>
+        <v>2542540.350000002</v>
       </c>
       <c r="K5" t="n">
-        <v>1327</v>
+        <v>1376</v>
       </c>
       <c r="L5" t="n">
-        <v>18830.08</v>
+        <v>2026853.8</v>
       </c>
       <c r="M5" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -644,40 +644,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1185116.01</v>
+        <v>3419259.209999999</v>
       </c>
       <c r="C6" t="n">
-        <v>1298</v>
+        <v>1483</v>
       </c>
       <c r="D6" t="n">
-        <v>972923.4899999981</v>
+        <v>3238354.949999998</v>
       </c>
       <c r="E6" t="n">
-        <v>1271</v>
+        <v>1458</v>
       </c>
       <c r="F6" t="n">
-        <v>212192.52</v>
+        <v>180904.26</v>
       </c>
       <c r="G6" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H6" t="n">
-        <v>857460.2199999997</v>
+        <v>800664.3899999992</v>
       </c>
       <c r="I6" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J6" t="n">
-        <v>327655.7900000004</v>
+        <v>2618594.819999998</v>
       </c>
       <c r="K6" t="n">
-        <v>1178</v>
+        <v>1364</v>
       </c>
       <c r="L6" t="n">
-        <v>18413.58000000001</v>
+        <v>2026152.95</v>
       </c>
       <c r="M6" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -687,40 +687,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1156915.85</v>
+        <v>3217276.409999997</v>
       </c>
       <c r="C7" t="n">
-        <v>1209</v>
+        <v>1307</v>
       </c>
       <c r="D7" t="n">
-        <v>972335.7900000005</v>
+        <v>2990604.539999996</v>
       </c>
       <c r="E7" t="n">
-        <v>1176</v>
+        <v>1282</v>
       </c>
       <c r="F7" t="n">
-        <v>184580.06</v>
+        <v>226671.8700000001</v>
       </c>
       <c r="G7" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="H7" t="n">
-        <v>872389.45</v>
+        <v>853465.1099999999</v>
       </c>
       <c r="I7" t="n">
         <v>117</v>
       </c>
       <c r="J7" t="n">
-        <v>284526.4000000008</v>
+        <v>2363811.300000002</v>
       </c>
       <c r="K7" t="n">
-        <v>1092</v>
+        <v>1190</v>
       </c>
       <c r="L7" t="n">
-        <v>18361.19</v>
+        <v>2025838.5</v>
       </c>
       <c r="M7" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -730,40 +730,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1226590.020000001</v>
+        <v>3235353.849999993</v>
       </c>
       <c r="C8" t="n">
-        <v>1435</v>
+        <v>1190</v>
       </c>
       <c r="D8" t="n">
-        <v>1054734.900000003</v>
+        <v>2962248.339999993</v>
       </c>
       <c r="E8" t="n">
-        <v>1404</v>
+        <v>1167</v>
       </c>
       <c r="F8" t="n">
-        <v>171855.1199999999</v>
+        <v>273105.5100000001</v>
       </c>
       <c r="G8" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H8" t="n">
-        <v>845689.2200000003</v>
+        <v>937016.62</v>
       </c>
       <c r="I8" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J8" t="n">
-        <v>380900.7999999997</v>
+        <v>2298337.230000002</v>
       </c>
       <c r="K8" t="n">
-        <v>1313</v>
+        <v>1073</v>
       </c>
       <c r="L8" t="n">
-        <v>20034.45</v>
+        <v>2025567.110000001</v>
       </c>
       <c r="M8" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
@@ -773,40 +773,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1199019.850000002</v>
+        <v>1233588.090000002</v>
       </c>
       <c r="C9" t="n">
-        <v>1433</v>
+        <v>1420</v>
       </c>
       <c r="D9" t="n">
-        <v>1024025.000000001</v>
+        <v>1017904.54</v>
       </c>
       <c r="E9" t="n">
-        <v>1403</v>
+        <v>1395</v>
       </c>
       <c r="F9" t="n">
-        <v>174994.8499999998</v>
+        <v>215683.5500000001</v>
       </c>
       <c r="G9" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="H9" t="n">
-        <v>816042.5000000006</v>
+        <v>846995.1099999995</v>
       </c>
       <c r="I9" t="n">
         <v>119</v>
       </c>
       <c r="J9" t="n">
-        <v>382977.3499999999</v>
+        <v>386592.9799999996</v>
       </c>
       <c r="K9" t="n">
-        <v>1314</v>
+        <v>1301</v>
       </c>
       <c r="L9" t="n">
-        <v>19911.35</v>
+        <v>28550.3</v>
       </c>
       <c r="M9" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -816,40 +816,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1235058.840000003</v>
+        <v>1257203.069999999</v>
       </c>
       <c r="C10" t="n">
-        <v>1443</v>
+        <v>1398</v>
       </c>
       <c r="D10" t="n">
-        <v>1044756.860000001</v>
+        <v>1040972.93</v>
       </c>
       <c r="E10" t="n">
-        <v>1413</v>
+        <v>1374</v>
       </c>
       <c r="F10" t="n">
-        <v>190301.9800000001</v>
+        <v>216230.1400000001</v>
       </c>
       <c r="G10" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="H10" t="n">
-        <v>837111.9800000001</v>
+        <v>826100.3099999996</v>
       </c>
       <c r="I10" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J10" t="n">
-        <v>397946.8599999999</v>
+        <v>431102.7600000001</v>
       </c>
       <c r="K10" t="n">
-        <v>1326</v>
+        <v>1279</v>
       </c>
       <c r="L10" t="n">
-        <v>20033.10999999999</v>
+        <v>28475.79</v>
       </c>
       <c r="M10" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -859,40 +859,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1274706.210000002</v>
+        <v>1275900.500000002</v>
       </c>
       <c r="C11" t="n">
-        <v>1437</v>
+        <v>1371</v>
       </c>
       <c r="D11" t="n">
-        <v>1073870.639999999</v>
+        <v>1086715.079999999</v>
       </c>
       <c r="E11" t="n">
-        <v>1408</v>
+        <v>1347</v>
       </c>
       <c r="F11" t="n">
-        <v>200835.5700000001</v>
+        <v>189185.4199999999</v>
       </c>
       <c r="G11" t="n">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="H11" t="n">
-        <v>865382.9099999986</v>
+        <v>814473.5499999993</v>
       </c>
       <c r="I11" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J11" t="n">
-        <v>409323.3000000003</v>
+        <v>461426.9500000005</v>
       </c>
       <c r="K11" t="n">
-        <v>1319</v>
+        <v>1255</v>
       </c>
       <c r="L11" t="n">
-        <v>19794.95</v>
+        <v>28580.80000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -904,6 +904,6 @@
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B1:C1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>